--- a/VerveStacks_IND_grids_kan60/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EA2AC4-9E25-4EC6-9107-5416F96FBBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B641B89-C32F-41F2-94B1-D6F39C6EF9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1302,13 +1302,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S2aH2,S3aH2</t>
+    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S1aH3,S3aH1,S3aH3,S4aH1,S2aH3,S1aH1,S4aH3</t>
+    <t>S2aH3,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3,S3aH1,S2aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S1aH3,S3aH1,S3aH3,S4aH1,S2aH3,S1aH1,S4aH3</v>
+        <v>S2aH3,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3,S3aH1,S2aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S2aH2,S3aH2</v>
+        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2016,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5FF716A-C8A9-4CB3-BBFC-4FAAB13F94D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65ED0619-B487-44E7-A783-2645DDA474C4}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2096,7 +2096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD553950-1882-48EF-8426-CB2FFE5CCA9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8150356B-54CF-45C6-B15E-251EF2B169FB}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28222,7 +28222,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E008057-E10D-4224-A692-93A38FAEE8E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E30CA0-F828-4E58-AF14-89AA611B7B18}">
   <dimension ref="B9:CI178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65653,7 +65653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B8A8CB-3EAE-4D33-98F3-DA36DCC0E675}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D972380F-3160-4AF7-9529-56DD98F1D1B9}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65760,7 +65760,7 @@
         <v>38</v>
       </c>
       <c r="R11">
-        <v>0.26990000000000003</v>
+        <v>0.26989999999999997</v>
       </c>
       <c r="S11" t="s">
         <v>431</v>
@@ -66024,7 +66024,7 @@
         <v>44</v>
       </c>
       <c r="R17">
-        <v>0.56513333333333338</v>
+        <v>0.56513333333333327</v>
       </c>
       <c r="S17" t="s">
         <v>431</v>
@@ -66313,7 +66313,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.5820333333333334</v>
+        <v>0.58203333333333329</v>
       </c>
       <c r="S25" t="s">
         <v>431</v>
@@ -66543,7 +66543,7 @@
         <v>38</v>
       </c>
       <c r="R35">
-        <v>0.22889999999999999</v>
+        <v>0.22890000000000002</v>
       </c>
       <c r="S35" t="s">
         <v>431</v>
@@ -66878,7 +66878,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.43829999999999997</v>
+        <v>0.43830000000000008</v>
       </c>
       <c r="S57" t="s">
         <v>431</v>
@@ -66962,7 +66962,7 @@
         <v>38</v>
       </c>
       <c r="R63">
-        <v>0.24303333333333335</v>
+        <v>0.24303333333333332</v>
       </c>
       <c r="S63" t="s">
         <v>431</v>
@@ -67018,7 +67018,7 @@
         <v>38</v>
       </c>
       <c r="R67">
-        <v>0.23089999999999999</v>
+        <v>0.23090000000000002</v>
       </c>
       <c r="S67" t="s">
         <v>431</v>
@@ -67298,7 +67298,7 @@
         <v>38</v>
       </c>
       <c r="R87">
-        <v>0.2869666666666667</v>
+        <v>0.28696666666666665</v>
       </c>
       <c r="S87" t="s">
         <v>431</v>
@@ -67326,7 +67326,7 @@
         <v>44</v>
       </c>
       <c r="R89">
-        <v>0.60863333333333336</v>
+        <v>0.60863333333333325</v>
       </c>
       <c r="S89" t="s">
         <v>431</v>
@@ -67410,7 +67410,7 @@
         <v>38</v>
       </c>
       <c r="R95">
-        <v>0.24973333333333333</v>
+        <v>0.24973333333333336</v>
       </c>
       <c r="S95" t="s">
         <v>431</v>
@@ -67494,7 +67494,7 @@
         <v>44</v>
       </c>
       <c r="R101">
-        <v>0.5054333333333334</v>
+        <v>0.50543333333333329</v>
       </c>
       <c r="S101" t="s">
         <v>431</v>
@@ -67802,7 +67802,7 @@
         <v>38</v>
       </c>
       <c r="R123">
-        <v>0.24543333333333331</v>
+        <v>0.24543333333333336</v>
       </c>
       <c r="S123" t="s">
         <v>431</v>
@@ -67830,7 +67830,7 @@
         <v>44</v>
       </c>
       <c r="R125">
-        <v>0.49769999999999998</v>
+        <v>0.49770000000000003</v>
       </c>
       <c r="S125" t="s">
         <v>431</v>

--- a/VerveStacks_IND_grids_kan60/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B641B89-C32F-41F2-94B1-D6F39C6EF9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58C5E2CF-451D-4BD6-A4CD-EFF0D837F0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1302,13 +1302,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S1aH2,S3aH2,S4aH2</t>
+    <t>S3aH2,S4aH2,S2aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3,S3aH1,S2aH1</t>
+    <t>S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH3,S4aH1,S1aH3,S1aH1,S4aH3,S3aH1,S2aH1</v>
+        <v>S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S1aH2,S3aH2,S4aH2</v>
+        <v>S3aH2,S4aH2,S2aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2016,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65ED0619-B487-44E7-A783-2645DDA474C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83A7344-1289-40FA-9089-090D3D8949A8}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2096,7 +2096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8150356B-54CF-45C6-B15E-251EF2B169FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7854D6-2BE5-49C1-B287-D8E7AEB036F7}">
   <dimension ref="B9:O946"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28222,7 +28222,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E30CA0-F828-4E58-AF14-89AA611B7B18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{979CE110-5D64-43B2-A80D-9F173E41DE6A}">
   <dimension ref="B9:CI178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65653,7 +65653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D972380F-3160-4AF7-9529-56DD98F1D1B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{706D6546-B50D-4382-B105-7F8554C815A7}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65804,7 +65804,7 @@
         <v>42</v>
       </c>
       <c r="R12">
-        <v>0.3469666666666667</v>
+        <v>0.34696666666666665</v>
       </c>
       <c r="S12" t="s">
         <v>431</v>
@@ -65892,7 +65892,7 @@
         <v>46</v>
       </c>
       <c r="R14">
-        <v>0.4371666666666667</v>
+        <v>0.43716666666666665</v>
       </c>
       <c r="S14" t="s">
         <v>431</v>
@@ -66024,7 +66024,7 @@
         <v>44</v>
       </c>
       <c r="R17">
-        <v>0.56513333333333327</v>
+        <v>0.56513333333333338</v>
       </c>
       <c r="S17" t="s">
         <v>431</v>
@@ -66156,7 +66156,7 @@
         <v>42</v>
       </c>
       <c r="R20">
-        <v>0.35463333333333336</v>
+        <v>0.3546333333333333</v>
       </c>
       <c r="S20" t="s">
         <v>431</v>
@@ -66200,7 +66200,7 @@
         <v>44</v>
       </c>
       <c r="R21">
-        <v>0.57656666666666678</v>
+        <v>0.57656666666666667</v>
       </c>
       <c r="S21" t="s">
         <v>431</v>
@@ -66290,7 +66290,7 @@
         <v>42</v>
       </c>
       <c r="R24">
-        <v>0.34206666666666669</v>
+        <v>0.34206666666666674</v>
       </c>
       <c r="S24" t="s">
         <v>431</v>
@@ -66313,7 +66313,7 @@
         <v>44</v>
       </c>
       <c r="R25">
-        <v>0.58203333333333329</v>
+        <v>0.5820333333333334</v>
       </c>
       <c r="S25" t="s">
         <v>431</v>
@@ -66336,7 +66336,7 @@
         <v>46</v>
       </c>
       <c r="R26">
-        <v>0.48209999999999997</v>
+        <v>0.48210000000000003</v>
       </c>
       <c r="S26" t="s">
         <v>431</v>
@@ -66382,7 +66382,7 @@
         <v>42</v>
       </c>
       <c r="R28">
-        <v>0.28320000000000006</v>
+        <v>0.28320000000000001</v>
       </c>
       <c r="S28" t="s">
         <v>431</v>
@@ -66428,7 +66428,7 @@
         <v>46</v>
       </c>
       <c r="R30">
-        <v>0.42013333333333341</v>
+        <v>0.4201333333333333</v>
       </c>
       <c r="S30" t="s">
         <v>431</v>
@@ -66497,7 +66497,7 @@
         <v>44</v>
       </c>
       <c r="R33">
-        <v>0.49940000000000001</v>
+        <v>0.4993999999999999</v>
       </c>
       <c r="S33" t="s">
         <v>431</v>
@@ -66566,7 +66566,7 @@
         <v>42</v>
       </c>
       <c r="R36">
-        <v>0.30336666666666662</v>
+        <v>0.30336666666666667</v>
       </c>
       <c r="S36" t="s">
         <v>431</v>
@@ -66724,7 +66724,7 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.37930000000000003</v>
+        <v>0.37929999999999997</v>
       </c>
       <c r="S46" t="s">
         <v>431</v>
@@ -66752,7 +66752,7 @@
         <v>42</v>
       </c>
       <c r="R48">
-        <v>0.28029999999999999</v>
+        <v>0.28030000000000005</v>
       </c>
       <c r="S48" t="s">
         <v>431</v>
@@ -66878,7 +66878,7 @@
         <v>44</v>
       </c>
       <c r="R57">
-        <v>0.43830000000000008</v>
+        <v>0.43829999999999997</v>
       </c>
       <c r="S57" t="s">
         <v>431</v>
@@ -66948,7 +66948,7 @@
         <v>46</v>
       </c>
       <c r="R62">
-        <v>0.40466666666666667</v>
+        <v>0.40466666666666673</v>
       </c>
       <c r="S62" t="s">
         <v>431</v>
@@ -66990,7 +66990,7 @@
         <v>44</v>
       </c>
       <c r="R65">
-        <v>0.47416666666666668</v>
+        <v>0.47416666666666663</v>
       </c>
       <c r="S65" t="s">
         <v>431</v>
@@ -67032,7 +67032,7 @@
         <v>42</v>
       </c>
       <c r="R68">
-        <v>0.27943333333333337</v>
+        <v>0.27943333333333331</v>
       </c>
       <c r="S68" t="s">
         <v>431</v>
@@ -67088,7 +67088,7 @@
         <v>42</v>
       </c>
       <c r="R72">
-        <v>0.31673333333333337</v>
+        <v>0.31673333333333331</v>
       </c>
       <c r="S72" t="s">
         <v>431</v>
@@ -67158,7 +67158,7 @@
         <v>44</v>
       </c>
       <c r="R77">
-        <v>0.48763333333333336</v>
+        <v>0.48763333333333331</v>
       </c>
       <c r="S77" t="s">
         <v>431</v>
@@ -67368,7 +67368,7 @@
         <v>42</v>
       </c>
       <c r="R92">
-        <v>0.3405333333333333</v>
+        <v>0.34053333333333335</v>
       </c>
       <c r="S92" t="s">
         <v>431</v>
@@ -67452,7 +67452,7 @@
         <v>46</v>
       </c>
       <c r="R98">
-        <v>0.49490000000000006</v>
+        <v>0.49489999999999995</v>
       </c>
       <c r="S98" t="s">
         <v>431</v>
@@ -67480,7 +67480,7 @@
         <v>42</v>
       </c>
       <c r="R100">
-        <v>0.31083333333333335</v>
+        <v>0.31083333333333329</v>
       </c>
       <c r="S100" t="s">
         <v>431</v>
@@ -67494,7 +67494,7 @@
         <v>44</v>
       </c>
       <c r="R101">
-        <v>0.50543333333333329</v>
+        <v>0.5054333333333334</v>
       </c>
       <c r="S101" t="s">
         <v>431</v>
@@ -67774,7 +67774,7 @@
         <v>44</v>
       </c>
       <c r="R121">
-        <v>0.49280000000000007</v>
+        <v>0.49279999999999996</v>
       </c>
       <c r="S121" t="s">
         <v>431</v>
@@ -67816,7 +67816,7 @@
         <v>42</v>
       </c>
       <c r="R124">
-        <v>0.29129999999999995</v>
+        <v>0.2913</v>
       </c>
       <c r="S124" t="s">
         <v>431</v>
